--- a/crafting/crafting_recipes.xlsx
+++ b/crafting/crafting_recipes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Idler\crafting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE89A3B0-FE6E-4DD0-87EB-003784B109CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E3B946-DEE5-4CF7-87A5-D2721B455141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="690" windowWidth="23040" windowHeight="12120" firstSheet="14" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="897" firstSheet="10" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Crafting Recipes" sheetId="1" r:id="rId1"/>
@@ -30,9 +30,9 @@
     <sheet name="Recipes_Amulets" sheetId="15" r:id="rId15"/>
     <sheet name="Recipes_Armor" sheetId="16" r:id="rId16"/>
     <sheet name="Recipes_Helmets" sheetId="17" r:id="rId17"/>
-    <sheet name="Recipes_Pants" sheetId="18" r:id="rId18"/>
-    <sheet name="Recipes_Boots" sheetId="19" r:id="rId19"/>
-    <sheet name="Recipes_Gloves" sheetId="20" r:id="rId20"/>
+    <sheet name="Recipes_Gloves" sheetId="20" r:id="rId18"/>
+    <sheet name="Recipes_Pants" sheetId="18" r:id="rId19"/>
+    <sheet name="Recipes_Boots" sheetId="19" r:id="rId20"/>
     <sheet name="Recipes_Shields" sheetId="21" r:id="rId21"/>
     <sheet name="GeneratorConfig" sheetId="22" r:id="rId22"/>
     <sheet name="Recipes_Staves" sheetId="23" r:id="rId23"/>
@@ -2791,6 +2791,9 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2815,9 +2818,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -11785,6 +11785,530 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <dimension ref="A1:T8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="9" max="9" width="8" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="13" max="13" width="8" customWidth="1"/>
+    <col min="14" max="14" width="30" customWidth="1"/>
+    <col min="15" max="15" width="8" customWidth="1"/>
+    <col min="16" max="16" width="15" customWidth="1"/>
+    <col min="17" max="17" width="17" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
+    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>372</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>373</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>374</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>375</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>376</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>377</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>378</v>
+      </c>
+      <c r="I1" s="39" t="s">
+        <v>379</v>
+      </c>
+      <c r="J1" s="39" t="s">
+        <v>380</v>
+      </c>
+      <c r="K1" s="39" t="s">
+        <v>381</v>
+      </c>
+      <c r="L1" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="N1" s="39" t="s">
+        <v>383</v>
+      </c>
+      <c r="O1" s="39" t="s">
+        <v>384</v>
+      </c>
+      <c r="P1" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q1" s="39" t="s">
+        <v>386</v>
+      </c>
+      <c r="R1" s="39" t="s">
+        <v>387</v>
+      </c>
+      <c r="S1" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="T1" s="39" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>664</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>565</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>665</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>609</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="G2" s="21">
+        <v>4</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="I2" s="21">
+        <v>4</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>704</v>
+      </c>
+      <c r="K2" s="21">
+        <v>8</v>
+      </c>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="O2" s="21">
+        <v>6</v>
+      </c>
+      <c r="P2" s="21">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="21">
+        <v>1</v>
+      </c>
+      <c r="R2" s="21">
+        <v>65</v>
+      </c>
+      <c r="S2" s="21">
+        <v>25</v>
+      </c>
+      <c r="T2" s="21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>666</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>667</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>610</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="G3" s="21">
+        <v>5</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="I3" s="21">
+        <v>5</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>533</v>
+      </c>
+      <c r="K3" s="21">
+        <v>8</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="M3" s="21">
+        <v>1</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="O3" s="21">
+        <v>8</v>
+      </c>
+      <c r="P3" s="21">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="21">
+        <v>5</v>
+      </c>
+      <c r="R3" s="21">
+        <v>210</v>
+      </c>
+      <c r="S3" s="21">
+        <v>50</v>
+      </c>
+      <c r="T3" s="21">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>668</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>669</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>611</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="G4" s="21">
+        <v>5</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="I4" s="21">
+        <v>5</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>464</v>
+      </c>
+      <c r="K4" s="21">
+        <v>6</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="M4" s="21">
+        <v>1</v>
+      </c>
+      <c r="N4" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="O4" s="21">
+        <v>6</v>
+      </c>
+      <c r="P4" s="21">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="21">
+        <v>10</v>
+      </c>
+      <c r="R4" s="21">
+        <v>550</v>
+      </c>
+      <c r="S4" s="21">
+        <v>85</v>
+      </c>
+      <c r="T4" s="21">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>670</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>668</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="G5" s="21">
+        <v>6</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>406</v>
+      </c>
+      <c r="I5" s="21">
+        <v>6</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>464</v>
+      </c>
+      <c r="K5" s="21">
+        <v>8</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="M5" s="21">
+        <v>1</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="O5" s="21">
+        <v>8</v>
+      </c>
+      <c r="P5" s="21">
+        <v>25</v>
+      </c>
+      <c r="Q5" s="21">
+        <v>15</v>
+      </c>
+      <c r="R5" s="21">
+        <v>1000</v>
+      </c>
+      <c r="S5" s="21">
+        <v>120</v>
+      </c>
+      <c r="T5" s="21">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>671</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>569</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>670</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="G6" s="21">
+        <v>6</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="I6" s="21">
+        <v>6</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>530</v>
+      </c>
+      <c r="K6" s="21">
+        <v>3</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="M6" s="21">
+        <v>1</v>
+      </c>
+      <c r="N6" s="21" t="s">
+        <v>435</v>
+      </c>
+      <c r="O6" s="21">
+        <v>5</v>
+      </c>
+      <c r="P6" s="21">
+        <v>30</v>
+      </c>
+      <c r="Q6" s="21">
+        <v>20</v>
+      </c>
+      <c r="R6" s="21">
+        <v>1650</v>
+      </c>
+      <c r="S6" s="21">
+        <v>140</v>
+      </c>
+      <c r="T6" s="21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>673</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="G7" s="21">
+        <v>7</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="I7" s="21">
+        <v>7</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>530</v>
+      </c>
+      <c r="K7" s="21">
+        <v>4</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="M7" s="21">
+        <v>1</v>
+      </c>
+      <c r="N7" s="21" t="s">
+        <v>435</v>
+      </c>
+      <c r="O7" s="21">
+        <v>7</v>
+      </c>
+      <c r="P7" s="21">
+        <v>40</v>
+      </c>
+      <c r="Q7" s="21">
+        <v>25</v>
+      </c>
+      <c r="R7" s="21">
+        <v>1500</v>
+      </c>
+      <c r="S7" s="21">
+        <v>140</v>
+      </c>
+      <c r="T7" s="21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>675</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>571</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>612</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="G8" s="21">
+        <v>8</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="I8" s="21">
+        <v>8</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>472</v>
+      </c>
+      <c r="K8" s="21">
+        <v>4</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="M8" s="21">
+        <v>1</v>
+      </c>
+      <c r="N8" s="21" t="s">
+        <v>421</v>
+      </c>
+      <c r="O8" s="21">
+        <v>6</v>
+      </c>
+      <c r="P8" s="21">
+        <v>50</v>
+      </c>
+      <c r="Q8" s="21">
+        <v>30</v>
+      </c>
+      <c r="R8" s="21">
+        <v>5000</v>
+      </c>
+      <c r="S8" s="21">
+        <v>220</v>
+      </c>
+      <c r="T8" s="21">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:T8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12308,7 +12832,60 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="B2:B9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="75.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:T9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12828,597 +13405,20 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="54"/>
-      <c r="B9" s="54"/>
+      <c r="A9" s="40"/>
+      <c r="B9" s="40"/>
       <c r="D9" s="21"/>
-      <c r="F9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="J9" s="54"/>
-      <c r="L9" s="54"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="54"/>
-      <c r="Q9" s="54"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="54"/>
-      <c r="T9" s="54"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="75.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:T8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="9" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="30" customWidth="1"/>
-    <col min="11" max="11" width="8" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
-    <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="30" customWidth="1"/>
-    <col min="15" max="15" width="8" customWidth="1"/>
-    <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="17" customWidth="1"/>
-    <col min="18" max="18" width="12" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="20" max="20" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="39" t="s">
-        <v>372</v>
-      </c>
-      <c r="C1" s="39" t="s">
-        <v>373</v>
-      </c>
-      <c r="D1" s="39" t="s">
-        <v>374</v>
-      </c>
-      <c r="E1" s="39" t="s">
-        <v>375</v>
-      </c>
-      <c r="F1" s="39" t="s">
-        <v>376</v>
-      </c>
-      <c r="G1" s="39" t="s">
-        <v>377</v>
-      </c>
-      <c r="H1" s="39" t="s">
-        <v>378</v>
-      </c>
-      <c r="I1" s="39" t="s">
-        <v>379</v>
-      </c>
-      <c r="J1" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="K1" s="39" t="s">
-        <v>381</v>
-      </c>
-      <c r="L1" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="39" t="s">
-        <v>382</v>
-      </c>
-      <c r="N1" s="39" t="s">
-        <v>383</v>
-      </c>
-      <c r="O1" s="39" t="s">
-        <v>384</v>
-      </c>
-      <c r="P1" s="39" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q1" s="39" t="s">
-        <v>386</v>
-      </c>
-      <c r="R1" s="39" t="s">
-        <v>387</v>
-      </c>
-      <c r="S1" s="39" t="s">
-        <v>388</v>
-      </c>
-      <c r="T1" s="39" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>664</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>565</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>665</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>609</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="G2" s="21">
-        <v>4</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="I2" s="21">
-        <v>4</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>704</v>
-      </c>
-      <c r="K2" s="21">
-        <v>8</v>
-      </c>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21" t="s">
-        <v>425</v>
-      </c>
-      <c r="O2" s="21">
-        <v>6</v>
-      </c>
-      <c r="P2" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="21">
-        <v>1</v>
-      </c>
-      <c r="R2" s="21">
-        <v>65</v>
-      </c>
-      <c r="S2" s="21">
-        <v>25</v>
-      </c>
-      <c r="T2" s="21">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>666</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>566</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>667</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>610</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="G3" s="21">
-        <v>5</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>398</v>
-      </c>
-      <c r="I3" s="21">
-        <v>5</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>533</v>
-      </c>
-      <c r="K3" s="21">
-        <v>8</v>
-      </c>
-      <c r="L3" s="21" t="s">
-        <v>399</v>
-      </c>
-      <c r="M3" s="21">
-        <v>1</v>
-      </c>
-      <c r="N3" s="21" t="s">
-        <v>425</v>
-      </c>
-      <c r="O3" s="21">
-        <v>8</v>
-      </c>
-      <c r="P3" s="21">
-        <v>10</v>
-      </c>
-      <c r="Q3" s="21">
-        <v>5</v>
-      </c>
-      <c r="R3" s="21">
-        <v>210</v>
-      </c>
-      <c r="S3" s="21">
-        <v>50</v>
-      </c>
-      <c r="T3" s="21">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>668</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>567</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>669</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>611</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>398</v>
-      </c>
-      <c r="G4" s="21">
-        <v>5</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="I4" s="21">
-        <v>5</v>
-      </c>
-      <c r="J4" s="21" t="s">
-        <v>464</v>
-      </c>
-      <c r="K4" s="21">
-        <v>6</v>
-      </c>
-      <c r="L4" s="21" t="s">
-        <v>399</v>
-      </c>
-      <c r="M4" s="21">
-        <v>1</v>
-      </c>
-      <c r="N4" s="21" t="s">
-        <v>431</v>
-      </c>
-      <c r="O4" s="21">
-        <v>6</v>
-      </c>
-      <c r="P4" s="21">
-        <v>20</v>
-      </c>
-      <c r="Q4" s="21">
-        <v>10</v>
-      </c>
-      <c r="R4" s="21">
-        <v>550</v>
-      </c>
-      <c r="S4" s="21">
-        <v>85</v>
-      </c>
-      <c r="T4" s="21">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>670</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>568</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>668</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>567</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="G5" s="21">
-        <v>6</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>406</v>
-      </c>
-      <c r="I5" s="21">
-        <v>6</v>
-      </c>
-      <c r="J5" s="21" t="s">
-        <v>464</v>
-      </c>
-      <c r="K5" s="21">
-        <v>8</v>
-      </c>
-      <c r="L5" s="21" t="s">
-        <v>407</v>
-      </c>
-      <c r="M5" s="21">
-        <v>1</v>
-      </c>
-      <c r="N5" s="21" t="s">
-        <v>431</v>
-      </c>
-      <c r="O5" s="21">
-        <v>8</v>
-      </c>
-      <c r="P5" s="21">
-        <v>25</v>
-      </c>
-      <c r="Q5" s="21">
-        <v>15</v>
-      </c>
-      <c r="R5" s="21">
-        <v>1000</v>
-      </c>
-      <c r="S5" s="21">
-        <v>120</v>
-      </c>
-      <c r="T5" s="21">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>671</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>569</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>670</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>568</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="G6" s="21">
-        <v>6</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I6" s="21">
-        <v>6</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>530</v>
-      </c>
-      <c r="K6" s="21">
-        <v>3</v>
-      </c>
-      <c r="L6" s="21" t="s">
-        <v>407</v>
-      </c>
-      <c r="M6" s="21">
-        <v>1</v>
-      </c>
-      <c r="N6" s="21" t="s">
-        <v>435</v>
-      </c>
-      <c r="O6" s="21">
-        <v>5</v>
-      </c>
-      <c r="P6" s="21">
-        <v>30</v>
-      </c>
-      <c r="Q6" s="21">
-        <v>20</v>
-      </c>
-      <c r="R6" s="21">
-        <v>1650</v>
-      </c>
-      <c r="S6" s="21">
-        <v>140</v>
-      </c>
-      <c r="T6" s="21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>672</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>570</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>673</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>674</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="G7" s="21">
-        <v>7</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>414</v>
-      </c>
-      <c r="I7" s="21">
-        <v>7</v>
-      </c>
-      <c r="J7" s="21" t="s">
-        <v>530</v>
-      </c>
-      <c r="K7" s="21">
-        <v>4</v>
-      </c>
-      <c r="L7" s="21" t="s">
-        <v>415</v>
-      </c>
-      <c r="M7" s="21">
-        <v>1</v>
-      </c>
-      <c r="N7" s="21" t="s">
-        <v>435</v>
-      </c>
-      <c r="O7" s="21">
-        <v>7</v>
-      </c>
-      <c r="P7" s="21">
-        <v>40</v>
-      </c>
-      <c r="Q7" s="21">
-        <v>25</v>
-      </c>
-      <c r="R7" s="21">
-        <v>1500</v>
-      </c>
-      <c r="S7" s="21">
-        <v>140</v>
-      </c>
-      <c r="T7" s="21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>675</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>571</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>676</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>612</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="G8" s="21">
-        <v>8</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>418</v>
-      </c>
-      <c r="I8" s="21">
-        <v>8</v>
-      </c>
-      <c r="J8" s="21" t="s">
-        <v>472</v>
-      </c>
-      <c r="K8" s="21">
-        <v>4</v>
-      </c>
-      <c r="L8" s="21" t="s">
-        <v>420</v>
-      </c>
-      <c r="M8" s="21">
-        <v>1</v>
-      </c>
-      <c r="N8" s="21" t="s">
-        <v>421</v>
-      </c>
-      <c r="O8" s="21">
-        <v>6</v>
-      </c>
-      <c r="P8" s="21">
-        <v>50</v>
-      </c>
-      <c r="Q8" s="21">
-        <v>30</v>
-      </c>
-      <c r="R8" s="21">
-        <v>5000</v>
-      </c>
-      <c r="S8" s="21">
-        <v>220</v>
-      </c>
-      <c r="T8" s="21">
-        <v>24</v>
-      </c>
+      <c r="F9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="40"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17407,66 +17407,66 @@
   <sheetData>
     <row r="1" spans="2:55" s="1" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:55" s="1" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="43"/>
       <c r="J2" s="8"/>
       <c r="K2" s="9"/>
-      <c r="M2" s="40" t="s">
+      <c r="M2" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="42"/>
-      <c r="X2" s="43" t="s">
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="42"/>
+      <c r="V2" s="43"/>
+      <c r="X2" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="44"/>
-      <c r="AA2" s="44"/>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="44"/>
-      <c r="AD2" s="44"/>
-      <c r="AE2" s="44"/>
-      <c r="AF2" s="44"/>
-      <c r="AG2" s="45"/>
-      <c r="AI2" s="40" t="s">
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="45"/>
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="45"/>
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="45"/>
+      <c r="AG2" s="46"/>
+      <c r="AI2" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="41"/>
-      <c r="AL2" s="41"/>
-      <c r="AM2" s="41"/>
-      <c r="AN2" s="41"/>
-      <c r="AO2" s="41"/>
-      <c r="AP2" s="41"/>
-      <c r="AQ2" s="41"/>
-      <c r="AR2" s="42"/>
-      <c r="AT2" s="40" t="s">
+      <c r="AJ2" s="42"/>
+      <c r="AK2" s="42"/>
+      <c r="AL2" s="42"/>
+      <c r="AM2" s="42"/>
+      <c r="AN2" s="42"/>
+      <c r="AO2" s="42"/>
+      <c r="AP2" s="42"/>
+      <c r="AQ2" s="42"/>
+      <c r="AR2" s="43"/>
+      <c r="AT2" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="AU2" s="41"/>
-      <c r="AV2" s="41"/>
-      <c r="AW2" s="41"/>
-      <c r="AX2" s="41"/>
-      <c r="AY2" s="41"/>
-      <c r="AZ2" s="41"/>
-      <c r="BA2" s="41"/>
-      <c r="BB2" s="41"/>
-      <c r="BC2" s="42"/>
+      <c r="AU2" s="42"/>
+      <c r="AV2" s="42"/>
+      <c r="AW2" s="42"/>
+      <c r="AX2" s="42"/>
+      <c r="AY2" s="42"/>
+      <c r="AZ2" s="42"/>
+      <c r="BA2" s="42"/>
+      <c r="BB2" s="42"/>
+      <c r="BC2" s="43"/>
     </row>
     <row r="3" spans="2:55" s="1" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="15" t="s">
@@ -19757,16 +19757,16 @@
     </row>
     <row r="18" spans="2:55" ht="9.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:55" x14ac:dyDescent="0.3">
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="43"/>
       <c r="J19" s="8"/>
       <c r="K19" s="9"/>
     </row>
@@ -20300,30 +20300,30 @@
   <sheetData>
     <row r="1" spans="2:22" ht="9.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:22" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
+      <c r="M2" s="47" t="s">
         <v>319</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="49"/>
     </row>
     <row r="3" spans="2:22" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
@@ -21257,18 +21257,18 @@
     </row>
     <row r="18" spans="2:22" ht="9.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:22" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="49"/>
     </row>
     <row r="20" spans="2:22" ht="10.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
@@ -21779,18 +21779,18 @@
   <sheetData>
     <row r="1" spans="2:13" ht="9.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:13" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="52"/>
     </row>
     <row r="3" spans="2:13" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
@@ -22287,61 +22287,61 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="54" t="s">
         <v>366</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="53" t="s">
         <v>367</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="53" t="s">
         <v>368</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="53" t="s">
         <v>369</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="53" t="s">
         <v>370</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="53" t="s">
         <v>371</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="6">
